--- a/Cosas que llegan de mercado/2026/Periodo 1/Nota4.xlsx
+++ b/Cosas que llegan de mercado/2026/Periodo 1/Nota4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\GitHub\Motozom\Cosas que llegan de mercado\2026\Periodo 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3C56945-F089-481B-8B91-71A77860C5ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3133486-20D6-4076-82AF-052602A5E69F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Llego bien?</t>
   </si>
@@ -43,6 +43,9 @@
   </si>
   <si>
     <t>SI LLEGO COMPLETO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NO SE ENCARGARON </t>
   </si>
 </sst>
 </file>
@@ -513,7 +516,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="12:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="12:15" x14ac:dyDescent="0.25">
       <c r="L23">
         <v>450</v>
       </c>
@@ -523,6 +526,9 @@
       <c r="N23">
         <f>L23*M23</f>
         <v>900</v>
+      </c>
+      <c r="O23" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
